--- a/浙江交通集团_知识图谱数据.xlsx
+++ b/浙江交通集团_知识图谱数据.xlsx
@@ -46,7 +46,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +89,12 @@
         <bgColor rgb="00ffad5c"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ff6b6b"/>
+        <bgColor rgb="00ff6b6b"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -140,6 +146,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -516,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -874,59 +883,55 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>gx</t>
+          <t>t</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>公司节点</t>
+          <t>板块节点</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>浙江高信</t>
+          <t>创新特区</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>数字化平台</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+          <t>新增长极</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>创</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>数字基建,数据服务</t>
+          <t>前沿技术,成果转化</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>集团交通信息与数字化业务发展平台。</t>
+          <t>聚焦前沿技术研发与产业化应用，打造创新驱动新引擎。</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>提供智慧交通规划、数字基础设施和数据增值服务。</t>
+          <t>开展新技术、新产业、新模式的探索与孵化。</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>让出行更便捷，让生活更美好。</t>
+          <t>敢为人先，追求卓越。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>sj</t>
+          <t>gx</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -936,12 +941,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>数智交院</t>
+          <t>浙江高信</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>工程科技咨询</t>
+          <t>数字化平台</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -951,34 +956,34 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>数</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>规划设计,科技研发</t>
+          <t>数字基建,数据服务</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>集规划、勘察、设计、检测和科技数字化于一体。</t>
+          <t>集团交通信息与数字化业务发展平台。</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>开展综合交通规划、工程咨询、检测和数字化研发。</t>
+          <t>提供智慧交通规划、数字基础设施和数据增值服务。</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>路更畅，城更美 · 知行合一，追求卓越。</t>
+          <t>让出行更便捷，让生活更美好。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>hh</t>
+          <t>sj</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -988,49 +993,49 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>浙江沪杭甬</t>
+          <t>数智交院</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>高速运营</t>
+          <t>工程科技咨询</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>s</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>路</t>
+          <t>数</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>高速运营,上市公司</t>
+          <t>规划设计,科技研发</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>浙江省第一家高速公路专业化运营企业。</t>
+          <t>集规划、勘察、设计、检测和科技数字化于一体。</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>开展高速公路投资、建设、运营和养护。</t>
+          <t>开展综合交通规划、工程咨询、检测和数字化研发。</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>畅行美好生活，服务交通强国。</t>
+          <t>路更畅，城更美 · 知行合一，追求卓越。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>jg</t>
+          <t>hh</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1040,12 +1045,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>浙江交工</t>
+          <t>浙江沪杭甬</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>工程建设</t>
+          <t>高速运营</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1055,34 +1060,34 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>工</t>
+          <t>路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>工程施工,桥隧建设</t>
+          <t>高速运营,上市公司</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>集团交通工程建设重要专业力量。</t>
+          <t>浙江省第一家高速公路专业化运营企业。</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>承担公路、桥梁、隧道和市政工程建设。</t>
+          <t>开展高速公路投资、建设、运营和养护。</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>匠心筑路，品质致远。</t>
+          <t>畅行美好生活，服务交通强国。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>zt</t>
+          <t>jg</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1092,49 +1097,49 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>浙商中拓</t>
+          <t>浙江交工</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>供应链服务</t>
+          <t>工程建设</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>拓</t>
+          <t>工</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>供应链,产业金融</t>
+          <t>工程施工,桥隧建设</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>集团控股的供应链集成服务上市公司。</t>
+          <t>集团交通工程建设重要专业力量。</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>提供采购、库存、销售、物流、风险管理和产业金融服务。</t>
+          <t>承担公路、桥梁、隧道和市政工程建设。</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>创业、创新、创效 · 让产业链更集约更高效。</t>
+          <t>匠心筑路，品质致远。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>wl</t>
+          <t>zt</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1144,12 +1149,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>交投物流集团</t>
+          <t>浙商中拓</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>现代物流</t>
+          <t>供应链服务</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1159,34 +1164,34 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>物</t>
+          <t>拓</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>智慧园区,数智运输</t>
+          <t>供应链,产业金融</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>建设线上线下一体化综合物流服务体系。</t>
+          <t>集团控股的供应链集成服务上市公司。</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>整合货源、运力、仓储、金融及后服务资源。</t>
+          <t>提供采购、库存、销售、物流、风险管理和产业金融服务。</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>数智链接资源，高效服务产业。</t>
+          <t>创业、创新、创效 · 让产业链更集约更高效。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>zq</t>
+          <t>wl</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1196,49 +1201,49 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>浙商证券</t>
+          <t>交投物流集团</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>综合金融</t>
+          <t>现代物流</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>l</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>证</t>
+          <t>物</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>证券,财富管理</t>
+          <t>智慧园区,数智运输</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>浙江省首家国有控股上市券商。</t>
+          <t>建设线上线下一体化综合物流服务体系。</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>提供财富管理、投资银行、资管和机构金融服务。</t>
+          <t>整合货源、运力、仓储、金融及后服务资源。</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>同创、同享、同成长。</t>
+          <t>数智链接资源，高效服务产业。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>bx</t>
+          <t>zq</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1248,12 +1253,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>浙商保险</t>
+          <t>浙商证券</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>风险保障</t>
+          <t>综合金融</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1263,34 +1268,34 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>保</t>
+          <t>证</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>保险,风险保障</t>
+          <t>证券,财富管理</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>总部位于杭州的全国性综合财产保险公司。</t>
+          <t>浙江省首家国有控股上市券商。</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>提供车辆、企财、责任及工程保险服务。</t>
+          <t>提供财富管理、投资银行、资管和机构金融服务。</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>诚信相伴，托付永远 · 同责、同心、同创。</t>
+          <t>同创、同享、同成长。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>zy</t>
+          <t>bx</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1300,94 +1305,250 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>镇洋发展</t>
+          <t>浙商保险</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>绿色新材料</t>
+          <t>风险保障</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>f</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>镇</t>
+          <t>保</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>绿色化工,新材料</t>
+          <t>保险,风险保障</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>集团控股的绿色化工新材料上市公司。</t>
+          <t>总部位于杭州的全国性综合财产保险公司。</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>开展氯碱化工、有机化工和新材料研发生产。</t>
+          <t>提供车辆、企财、责任及工程保险服务。</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>规范、尽职、创新、进取。</t>
+          <t>诚信相伴，托付永远 · 同责、同心、同创。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>zy</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>公司节点</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>镇洋发展</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>绿色新材料</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>镇</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>绿色化工,新材料</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>集团控股的绿色化工新材料上市公司。</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>开展氯碱化工、有机化工和新材料研发生产。</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>规范、尽职、创新、进取。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>zyy</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>公司节点</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>交通资源集团</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>资源运营</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>资</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>矿产资源,绿色矿山</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>形成矿产资源、沥青和交通建材产业格局。</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>布局矿产资源、沥青、交通建材及绿色矿山运营。</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>创新有限资源价值，共育行业无限未来。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>jszy</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>公司节点</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>技术总院</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>前沿技术研发</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>研</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>人工智能,大数据,新能源</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>集团前沿技术研发与创新孵化平台。</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>开展人工智能、大数据、新能源等关键技术研发与成果转化。</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>创新驱动，引领未来。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>公司节点</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>测试节点</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>测试用临时节点</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>测</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>测试,临时</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>这是一个用于测试的临时节点。</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>用于验证导入功能。</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>测试文化。</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1540,6 +1701,28 @@
       <c r="D6" s="8" t="inlineStr">
         <is>
           <t>#ffad5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>创新特区</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>创新</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>#ff6b6b</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1667,17 +1850,17 @@
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>root</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>gx</t>
+          <t>t</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1872,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>sj</t>
+          <t>gx</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1701,12 +1884,12 @@
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>s</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>hh</t>
+          <t>sj</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1723,7 +1906,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>jg</t>
+          <t>hh</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1735,12 +1918,12 @@
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>i</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>zt</t>
+          <t>jg</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1757,7 +1940,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>wl</t>
+          <t>zt</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1769,12 +1952,12 @@
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>l</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>zq</t>
+          <t>wl</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1791,7 +1974,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>bx</t>
+          <t>zq</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1803,12 +1986,12 @@
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>f</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>zy</t>
+          <t>bx</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1825,10 +2008,61 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>zy</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
           <t>zyy</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>jszy</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1845,191 +2079,167 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>📋 浙江交通集团 · 企业文化知识图谱</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="10" t="inlineStr"/>
+      <c r="A2" s="11" t="inlineStr"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>【数据导入说明】</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>本Excel文件用于导入知识图谱系统，包含3个核心工作表：</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="10" t="inlineStr"/>
+      <c r="A5" s="11" t="inlineStr"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>1. 节点总览 — 定义所有节点实体</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 节点ID: 唯一标识，建议使用英文字母或拼音缩写</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 节点类型: 根节点 / 板块节点 / 公司节点</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 所属板块: 填写板块ID（s/i/l/f/n），仅公司节点需要</t>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 所属板块: 填写板块ID（s/i/l/f/n/t），仅公司节点需要</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 标签: 多个标签用英文逗号分隔</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="10" t="inlineStr"/>
+      <c r="A11" s="11" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>2. 板块配置 — 定义五大板块</t>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>2. 板块配置 — 定义六大板块</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 板块ID: s(智慧交通) / i(新基建) / l(新供应链) / f(新金融) / n(新产业)</t>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 板块ID: s(智慧交通) / i(新基建) / l(新供应链) / f(新金融) / n(新产业) / t(创新特区)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 颜色值: 十六进制颜色代码，如 #36d7e7</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="10" t="inlineStr"/>
+      <c r="A15" s="11" t="inlineStr"/>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>3. 连线关系 — 定义节点之间的连接</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 起点ID/终点ID: 必须与节点总览中的ID匹配</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 是否主线: 是/否，主线会以粗线高亮显示</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="10" t="inlineStr"/>
+      <c r="A19" s="11" t="inlineStr"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>【连线规则 - 重要】</t>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>【新增内容】</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>• 根节点(root) 必须连接所有板块节点(s/i/l/f/n) — 设置为「是」</t>
+          <t>• 新增板块：创新特区 (id=t, 颜色=#ff6b6b)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>• 每个板块节点 必须连接其下属公司节点 — 设置为「否」</t>
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>• 新增公司：技术总院 (id=jszy, 所属板块=t)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="10" t="inlineStr"/>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>• 新增测试节点：测试节点 (id=test, 所属板块=s) —— 用于测试导入功能</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>【扩展方法】</t>
-        </is>
-      </c>
+      <c r="A24" s="11" t="inlineStr"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>· 添加新公司: 在「节点总览」末尾新增行，指定所属板块</t>
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>生成时间: 2026年7月</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>· 添加新板块: 在「节点总览」和「板块配置」中同步添加</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>· 添加连线: 在「连线关系」中新增行</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>生成时间: 2026年7月</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>数据版本: v2.0 (修复连线问题)</t>
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>数据版本: v3.0 (含测试节点)</t>
         </is>
       </c>
     </row>

--- a/浙江交通集团_知识图谱数据.xlsx
+++ b/浙江交通集团_知识图谱数据.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97513\Desktop\github\CICORE_KG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A050F239-B1B9-4F34-8833-EBA5F3768B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{057359E6-78C7-4238-BE3E-C5A4F44C3B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3051" yWindow="3969" windowWidth="18515" windowHeight="11511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15943" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="节点总览" sheetId="1" r:id="rId1"/>
@@ -248,9 +248,6 @@
     <t>国际海运,航运物流,供应链管理,绿色航运</t>
   </si>
   <si>
-    <t>image/hy-bg.png</t>
-  </si>
-  <si>
     <t>zt</t>
   </si>
   <si>
@@ -260,9 +257,6 @@
     <t>供应链集成,贸工一体,产业金融,数智供应链</t>
   </si>
   <si>
-    <t>image/zt-bg.webp</t>
-  </si>
-  <si>
     <t>gx</t>
   </si>
   <si>
@@ -270,9 +264,6 @@
   </si>
   <si>
     <t>智慧交通,数字基建,数据服务,人工智能</t>
-  </si>
-  <si>
-    <t>image/gx-bg.png</t>
   </si>
   <si>
     <t>csfz</t>
@@ -2839,7 +2830,16 @@
     <t>image/jinkong.jpg</t>
   </si>
   <si>
-    <t>image/logistics</t>
+    <t>image/logistics.jpg</t>
+  </si>
+  <si>
+    <t>image/hy-bg.jpg</t>
+  </si>
+  <si>
+    <t>image/zt-bg.jpg</t>
+  </si>
+  <si>
+    <t>image/gx-bg.jpg</t>
   </si>
 </sst>
 </file>
@@ -3455,16 +3455,16 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -3633,16 +3633,16 @@
         <v>37</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -3667,16 +3667,16 @@
         <v>40</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
@@ -3701,16 +3701,16 @@
         <v>43</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
@@ -3735,16 +3735,16 @@
         <v>46</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
@@ -3769,16 +3769,16 @@
         <v>49</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
@@ -3803,16 +3803,16 @@
         <v>52</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
@@ -3837,16 +3837,16 @@
         <v>55</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
@@ -3871,16 +3871,16 @@
         <v>58</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
@@ -3905,16 +3905,16 @@
         <v>61</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
@@ -3939,16 +3939,16 @@
         <v>64</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
@@ -3973,16 +3973,16 @@
         <v>67</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
@@ -4007,16 +4007,16 @@
         <v>70</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
@@ -4041,16 +4041,16 @@
         <v>73</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>74</v>
+        <v>231</v>
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
@@ -4058,13 +4058,13 @@
     </row>
     <row r="22" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>35</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="13" t="s">
@@ -4072,19 +4072,19 @@
       </c>
       <c r="F22" s="14"/>
       <c r="G22" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>78</v>
+        <v>232</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
@@ -4092,13 +4092,13 @@
     </row>
     <row r="23" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>35</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="13" t="s">
@@ -4106,19 +4106,19 @@
       </c>
       <c r="F23" s="14"/>
       <c r="G23" s="14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
@@ -4126,13 +4126,13 @@
     </row>
     <row r="24" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>35</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="13" t="s">
@@ -4140,19 +4140,19 @@
       </c>
       <c r="F24" s="14"/>
       <c r="G24" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
@@ -4160,13 +4160,13 @@
     </row>
     <row r="25" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B25" s="13" t="s">
         <v>35</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="13" t="s">
@@ -4174,19 +4174,19 @@
       </c>
       <c r="F25" s="14"/>
       <c r="G25" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
@@ -4194,13 +4194,13 @@
     </row>
     <row r="26" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>35</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="13" t="s">
@@ -4208,19 +4208,19 @@
       </c>
       <c r="F26" s="14"/>
       <c r="G26" s="14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
@@ -4228,13 +4228,13 @@
     </row>
     <row r="27" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>35</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="13" t="s">
@@ -4242,19 +4242,19 @@
       </c>
       <c r="F27" s="14"/>
       <c r="G27" s="14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
@@ -4262,13 +4262,13 @@
     </row>
     <row r="28" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B28" s="13" t="s">
         <v>35</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="13" t="s">
@@ -4276,19 +4276,19 @@
       </c>
       <c r="F28" s="14"/>
       <c r="G28" s="14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
@@ -4296,13 +4296,13 @@
     </row>
     <row r="29" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>35</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="13" t="s">
@@ -4310,19 +4310,19 @@
       </c>
       <c r="F29" s="14"/>
       <c r="G29" s="14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
@@ -4330,13 +4330,13 @@
     </row>
     <row r="30" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>35</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D30" s="13"/>
       <c r="E30" s="13" t="s">
@@ -4344,19 +4344,19 @@
       </c>
       <c r="F30" s="14"/>
       <c r="G30" s="14" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
@@ -4364,13 +4364,13 @@
     </row>
     <row r="31" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>35</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="13" t="s">
@@ -4378,19 +4378,19 @@
       </c>
       <c r="F31" s="14"/>
       <c r="G31" s="14" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
@@ -4398,13 +4398,13 @@
     </row>
     <row r="32" spans="1:14" ht="100.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="15" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>35</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="13" t="s">
@@ -4412,19 +4412,19 @@
       </c>
       <c r="F32" s="14"/>
       <c r="G32" s="14" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="5"/>
@@ -4432,13 +4432,13 @@
     </row>
     <row r="33" spans="1:11" ht="37.299999999999997" x14ac:dyDescent="0.3">
       <c r="A33" s="16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>35</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D33" s="15"/>
       <c r="E33" s="15" t="s">
@@ -4446,19 +4446,19 @@
       </c>
       <c r="F33" s="15"/>
       <c r="G33" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I33" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="K33" s="18" t="s">
         <v>218</v>
-      </c>
-      <c r="J33" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="K33" s="18" t="s">
-        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -4479,16 +4479,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -4499,10 +4499,10 @@
         <v>20</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -4513,10 +4513,10 @@
         <v>23</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -4527,10 +4527,10 @@
         <v>26</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -4541,10 +4541,10 @@
         <v>28</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -4555,10 +4555,10 @@
         <v>30</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -4569,10 +4569,10 @@
         <v>32</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -4590,13 +4590,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4607,7 +4607,7 @@
         <v>18</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4618,7 +4618,7 @@
         <v>22</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4629,7 +4629,7 @@
         <v>25</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4640,7 +4640,7 @@
         <v>27</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4651,7 +4651,7 @@
         <v>29</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4662,7 +4662,7 @@
         <v>31</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4670,10 +4670,10 @@
         <v>18</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4681,10 +4681,10 @@
         <v>18</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4692,10 +4692,10 @@
         <v>18</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4703,10 +4703,10 @@
         <v>18</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4714,10 +4714,10 @@
         <v>18</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4725,10 +4725,10 @@
         <v>22</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4736,10 +4736,10 @@
         <v>22</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4747,10 +4747,10 @@
         <v>22</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4758,10 +4758,10 @@
         <v>22</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4769,10 +4769,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4783,7 +4783,7 @@
         <v>65</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4794,7 +4794,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4805,7 +4805,7 @@
         <v>71</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4813,10 +4813,10 @@
         <v>25</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4827,7 +4827,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4838,7 +4838,7 @@
         <v>59</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4849,7 +4849,7 @@
         <v>62</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4860,7 +4860,7 @@
         <v>47</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4871,7 +4871,7 @@
         <v>50</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4882,7 +4882,7 @@
         <v>53</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4893,7 +4893,7 @@
         <v>34</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4904,7 +4904,7 @@
         <v>38</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4915,7 +4915,7 @@
         <v>41</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4926,7 +4926,7 @@
         <v>44</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.3">
@@ -4934,10 +4934,10 @@
         <v>22</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
@@ -4978,12 +4978,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/浙江交通集团_知识图谱数据.xlsx
+++ b/浙江交通集团_知识图谱数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97513\Desktop\github\CICORE_KG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{057359E6-78C7-4238-BE3E-C5A4F44C3B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F39597-056D-4154-AB22-5B315D2C0B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15943" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="260">
   <si>
     <t>节点ID</t>
   </si>
@@ -2840,6 +2840,84 @@
   </si>
   <si>
     <t>image/gx-bg.jpg</t>
+  </si>
+  <si>
+    <t>audio/root_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/jszy_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/sxjs_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/jkjy_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/cw_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/jh_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/jjjs_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/zy_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/zq_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/bx_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/jk_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/wl_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/zyy_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/hy_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/zt_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/gx_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/csfz_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/sy_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/jg_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/sj_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/jw_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/tljs_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/gdjt_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/js_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/gs_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/jkg_1.mp3</t>
   </si>
 </sst>
 </file>
@@ -3467,7 +3545,9 @@
         <v>221</v>
       </c>
       <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
+      <c r="M2" s="5" t="s">
+        <v>234</v>
+      </c>
       <c r="N2" s="5"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -3645,7 +3725,9 @@
         <v>222</v>
       </c>
       <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
+      <c r="M9" s="2" t="s">
+        <v>235</v>
+      </c>
       <c r="N9" s="5"/>
     </row>
     <row r="10" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -3679,7 +3761,9 @@
         <v>223</v>
       </c>
       <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
+      <c r="M10" s="2" t="s">
+        <v>236</v>
+      </c>
       <c r="N10" s="5"/>
     </row>
     <row r="11" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -3713,7 +3797,9 @@
         <v>224</v>
       </c>
       <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
+      <c r="M11" s="2" t="s">
+        <v>237</v>
+      </c>
       <c r="N11" s="5"/>
     </row>
     <row r="12" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -3747,7 +3833,9 @@
         <v>221</v>
       </c>
       <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
+      <c r="M12" s="2" t="s">
+        <v>238</v>
+      </c>
       <c r="N12" s="5"/>
     </row>
     <row r="13" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -3781,7 +3869,9 @@
         <v>225</v>
       </c>
       <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
+      <c r="M13" s="2" t="s">
+        <v>239</v>
+      </c>
       <c r="N13" s="5"/>
     </row>
     <row r="14" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -3815,7 +3905,9 @@
         <v>221</v>
       </c>
       <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
+      <c r="M14" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="N14" s="5"/>
     </row>
     <row r="15" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -3849,7 +3941,9 @@
         <v>226</v>
       </c>
       <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
+      <c r="M15" s="2" t="s">
+        <v>241</v>
+      </c>
       <c r="N15" s="5"/>
     </row>
     <row r="16" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -3883,7 +3977,9 @@
         <v>227</v>
       </c>
       <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
+      <c r="M16" s="2" t="s">
+        <v>242</v>
+      </c>
       <c r="N16" s="5"/>
     </row>
     <row r="17" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -3917,7 +4013,9 @@
         <v>228</v>
       </c>
       <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
+      <c r="M17" s="2" t="s">
+        <v>243</v>
+      </c>
       <c r="N17" s="5"/>
     </row>
     <row r="18" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -3951,7 +4049,9 @@
         <v>229</v>
       </c>
       <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
+      <c r="M18" s="2" t="s">
+        <v>244</v>
+      </c>
       <c r="N18" s="5"/>
     </row>
     <row r="19" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -3985,7 +4085,9 @@
         <v>230</v>
       </c>
       <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
+      <c r="M19" s="2" t="s">
+        <v>245</v>
+      </c>
       <c r="N19" s="5"/>
     </row>
     <row r="20" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -4019,7 +4121,9 @@
         <v>221</v>
       </c>
       <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
+      <c r="M20" s="2" t="s">
+        <v>246</v>
+      </c>
       <c r="N20" s="5"/>
     </row>
     <row r="21" spans="1:14" ht="107.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4053,7 +4157,9 @@
         <v>231</v>
       </c>
       <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
+      <c r="M21" s="13" t="s">
+        <v>247</v>
+      </c>
       <c r="N21" s="5"/>
     </row>
     <row r="22" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -4087,7 +4193,9 @@
         <v>232</v>
       </c>
       <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
+      <c r="M22" s="13" t="s">
+        <v>248</v>
+      </c>
       <c r="N22" s="5"/>
     </row>
     <row r="23" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -4121,7 +4229,9 @@
         <v>233</v>
       </c>
       <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
+      <c r="M23" s="13" t="s">
+        <v>249</v>
+      </c>
       <c r="N23" s="5"/>
     </row>
     <row r="24" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -4155,7 +4265,9 @@
         <v>83</v>
       </c>
       <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
+      <c r="M24" s="13" t="s">
+        <v>250</v>
+      </c>
       <c r="N24" s="5"/>
     </row>
     <row r="25" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -4189,7 +4301,9 @@
         <v>87</v>
       </c>
       <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
+      <c r="M25" s="13" t="s">
+        <v>251</v>
+      </c>
       <c r="N25" s="5"/>
     </row>
     <row r="26" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -4223,7 +4337,9 @@
         <v>91</v>
       </c>
       <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
+      <c r="M26" s="13" t="s">
+        <v>252</v>
+      </c>
       <c r="N26" s="5"/>
     </row>
     <row r="27" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -4257,7 +4373,9 @@
         <v>220</v>
       </c>
       <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
+      <c r="M27" s="13" t="s">
+        <v>253</v>
+      </c>
       <c r="N27" s="5"/>
     </row>
     <row r="28" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -4291,7 +4409,9 @@
         <v>98</v>
       </c>
       <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
+      <c r="M28" s="13" t="s">
+        <v>254</v>
+      </c>
       <c r="N28" s="5"/>
     </row>
     <row r="29" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -4325,7 +4445,9 @@
         <v>102</v>
       </c>
       <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
+      <c r="M29" s="13" t="s">
+        <v>255</v>
+      </c>
       <c r="N29" s="5"/>
     </row>
     <row r="30" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -4359,7 +4481,9 @@
         <v>219</v>
       </c>
       <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
+      <c r="M30" s="13" t="s">
+        <v>256</v>
+      </c>
       <c r="N30" s="5"/>
     </row>
     <row r="31" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
@@ -4393,7 +4517,9 @@
         <v>109</v>
       </c>
       <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
+      <c r="M31" s="13" t="s">
+        <v>257</v>
+      </c>
       <c r="N31" s="5"/>
     </row>
     <row r="32" spans="1:14" ht="100.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4427,10 +4553,12 @@
         <v>217</v>
       </c>
       <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
+      <c r="M32" s="15" t="s">
+        <v>258</v>
+      </c>
       <c r="N32" s="5"/>
     </row>
-    <row r="33" spans="1:11" ht="37.299999999999997" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" ht="37.299999999999997" x14ac:dyDescent="0.3">
       <c r="A33" s="16" t="s">
         <v>113</v>
       </c>
@@ -4459,6 +4587,9 @@
       </c>
       <c r="K33" s="18" t="s">
         <v>218</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/浙江交通集团_知识图谱数据.xlsx
+++ b/浙江交通集团_知识图谱数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97513\Desktop\github\CICORE_KG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F39597-056D-4154-AB22-5B315D2C0B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814304F7-41F7-4221-9D96-44632B061183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15943" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/浙江交通集团_知识图谱数据.xlsx
+++ b/浙江交通集团_知识图谱数据.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97513\Desktop\github\CICORE_KG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\12983\Desktop\CICORE_KG-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814304F7-41F7-4221-9D96-44632B061183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17454755-9D64-419A-8793-7474122AEC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15943" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="节点总览" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="273">
   <si>
     <t>节点ID</t>
   </si>
@@ -471,6 +471,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>浙江省属特大型国企</t>
     </r>
@@ -478,6 +479,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，资产超万亿，控股企业424家。作为</t>
     </r>
@@ -486,6 +488,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>省级交通投融资主平台</t>
     </r>
@@ -493,6 +496,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，全面支撑全省综合交通发展。</t>
     </r>
@@ -502,6 +506,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>形成</t>
     </r>
@@ -510,6 +515,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>智慧交通</t>
     </r>
@@ -517,6 +523,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">及新基建、新供应链、新金融、新产业 </t>
     </r>
@@ -525,6 +532,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“1+4”核心业务板块</t>
     </r>
@@ -532,6 +540,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，深度覆盖并赋能交通全产业链发展。</t>
     </r>
@@ -541,6 +550,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">秉持 </t>
     </r>
@@ -549,6 +559,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“同路同心、共创共享”</t>
     </r>
@@ -556,6 +567,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 核心理念，坚决贯彻省委省政府战略，勇当全省 </t>
     </r>
@@ -564,6 +576,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“重要窗口”建设先行者</t>
     </r>
@@ -571,16 +584,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团国有全资科研平台</t>
     </r>
@@ -588,6 +603,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，注册资本20亿元。主攻</t>
     </r>
@@ -596,6 +612,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>交通前沿技术</t>
     </r>
@@ -603,6 +620,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，贯通研发至产业化，打造</t>
     </r>
@@ -611,6 +629,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团科创策源地</t>
     </r>
@@ -618,15 +637,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>聚焦</t>
     </r>
@@ -635,6 +656,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>综合交通关键技术攻关</t>
     </r>
@@ -642,6 +664,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，搭建数字基础设施与场景应用，推进</t>
     </r>
@@ -650,6 +673,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>科研成果工程化与产业化</t>
     </r>
@@ -657,6 +681,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，打通创新全链条。</t>
     </r>
@@ -666,6 +691,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>以</t>
     </r>
@@ -674,6 +700,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>科技引领交通发展</t>
     </r>
@@ -681,6 +708,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>为使命，立足国有科创平台定位，响应创新驱动战略，目标建成</t>
     </r>
@@ -689,6 +717,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>世界一流技术创新中心</t>
     </r>
@@ -696,16 +725,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>省属重点公办技工院校</t>
     </r>
@@ -713,6 +744,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，隶属浙江交通集团。作为</t>
     </r>
@@ -721,6 +753,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>高技能人才培养基地</t>
     </r>
@@ -728,6 +761,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，主营技工教育与职业培训，赋能主业。</t>
     </r>
@@ -737,6 +771,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>打造专业市场化产业载体，统筹资源开展</t>
     </r>
@@ -745,6 +780,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>产教融合</t>
     </r>
@@ -752,6 +788,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，推行市场化运营，为集团及社会持续输送</t>
     </r>
@@ -760,6 +797,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>高素质商贸人才</t>
     </r>
@@ -767,15 +805,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">秉持 </t>
     </r>
@@ -784,6 +824,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“立德树人，技能报国”</t>
     </r>
@@ -791,6 +832,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 使命，深耕商贸服务类人才培育，深化校企协同，全力建设</t>
     </r>
@@ -799,6 +841,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>高水平特色技师学院</t>
     </r>
@@ -806,16 +849,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团人才发展综合服务平台</t>
     </r>
@@ -823,6 +868,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，承担干部教育、人才培养与人力资源共享功能，为集团建设</t>
     </r>
@@ -831,6 +877,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>世界一流企业提供支撑</t>
     </r>
@@ -838,15 +885,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>开展产业平台建设，统筹内外资源，推进市场化运营，坚持协同发展，依托数字化与机制创新</t>
     </r>
@@ -855,6 +904,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>培育人才新动能</t>
     </r>
@@ -862,15 +912,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">以 </t>
     </r>
@@ -879,6 +931,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“为交通育人才，为发展聚动能”</t>
     </r>
@@ -886,6 +939,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 为使命，立足三大平台定位，全力打造</t>
     </r>
@@ -894,6 +948,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>交通行业一流人才发展服务平台</t>
     </r>
@@ -901,16 +956,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团资金集中管理司库平台</t>
     </r>
@@ -918,6 +975,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，经批准设立的非银行金融机构。承担管钱省钱赚钱职能，有效</t>
     </r>
@@ -926,6 +984,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>防控集团流动性风险</t>
     </r>
@@ -933,15 +992,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>提供资金归集、结算、融资及票据服务，统筹资本运作，搭建全维度风险管控体系，以</t>
     </r>
@@ -950,6 +1011,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>数字科技赋能财资管理</t>
     </r>
@@ -957,15 +1019,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">秉持 </t>
     </r>
@@ -974,6 +1038,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“立足集团，服务集团”</t>
     </r>
@@ -981,6 +1046,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 使命，致力于打造交投产业银行、企业司库和财资智库，全面支撑主业高质量发展。</t>
     </r>
@@ -991,6 +1057,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团产业投资核心上市平台</t>
     </r>
@@ -998,6 +1065,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，主营电容器、电子元器件与新能源制造，归属新产业板块，培育</t>
     </r>
@@ -1006,6 +1074,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>新兴产业增长极</t>
     </r>
@@ -1013,15 +1082,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>自主研发生产铝电解、薄膜及超级电容器，产品应用于储能、新能源车等领域，联动资本技术资源</t>
     </r>
@@ -1030,6 +1101,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>补齐先进制造</t>
     </r>
@@ -1037,15 +1109,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">坚守 </t>
     </r>
@@ -1054,6 +1128,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“以科技制造服务产业升级”</t>
     </r>
@@ -1061,6 +1136,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 使命，聚力攻关核心电子技术，致力于打造</t>
     </r>
@@ -1069,6 +1145,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>具有国际竞争力的电子元器件</t>
     </r>
@@ -1076,16 +1153,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团全资市场化产业投资平台</t>
     </r>
@@ -1093,6 +1172,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，聚焦高端装备、新能源与人工智能等新兴产业，负责挖掘新兴赛道与</t>
     </r>
@@ -1101,6 +1181,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>培育产业主体</t>
     </r>
@@ -1108,15 +1189,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>深耕战略性产业投资，通过控股并购与产业基金联动多方资本，做好投后治理，依托交通场景</t>
     </r>
@@ -1125,6 +1208,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>落地转化科创成果</t>
     </r>
@@ -1132,15 +1216,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>以</t>
     </r>
@@ -1149,6 +1235,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>资本赋能集团新产业发展</t>
     </r>
@@ -1156,6 +1243,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>为使命，致力于建设具备强大产业投资能力、凸显交通产业特色的</t>
     </r>
@@ -1164,6 +1252,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>专业投资平台</t>
     </r>
@@ -1171,16 +1260,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团控股A股上市化工平台</t>
     </r>
@@ -1188,6 +1279,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，坐落宁波石化园区，主营氯碱、有机化工与新材料，持续推进混改与</t>
     </r>
@@ -1196,6 +1288,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>绿色低碳转型</t>
     </r>
@@ -1203,15 +1296,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>开展氯碱基础化工与新材料生产，依托临港优势开展供应链协同，借助上市平台实施资本运作，</t>
     </r>
@@ -1220,6 +1315,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>打造绿色智造</t>
     </r>
@@ -1227,15 +1323,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">践行 </t>
     </r>
@@ -1244,6 +1342,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“安全为先、成本领先、绿色低碳”</t>
     </r>
@@ -1251,6 +1350,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 理念，弘扬创新突破精神，聚力打造集团重要</t>
     </r>
@@ -1259,6 +1359,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>临港绿色石化产业基地</t>
     </r>
@@ -1266,16 +1367,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团控股全国性综合A股券商</t>
     </r>
@@ -1283,6 +1386,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，业务涵盖财富管理、投行、资管及期货等，是连接交通产业与</t>
     </r>
@@ -1291,6 +1395,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>多层次资本桥梁</t>
     </r>
@@ -1298,15 +1403,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>深耕专业金融服务，聚焦集团重大项目做好金融支撑，统筹融资与资产证券化，搭建全维度风控体系，</t>
     </r>
@@ -1315,6 +1422,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>打通产融</t>
     </r>
@@ -1322,15 +1430,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">秉持 </t>
     </r>
@@ -1339,6 +1449,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“汇聚财智，成就你我”</t>
     </r>
@@ -1346,6 +1457,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 使命，坚守诚实做人、踏实做事价值观，致力于打造</t>
     </r>
@@ -1354,6 +1466,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>最具浙商特色财富增值</t>
     </r>
@@ -1361,16 +1474,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>全国性综合财产保险公司</t>
     </r>
@@ -1378,6 +1493,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，成立于2009年，是集团金融板块服务实体经济、交通产业和</t>
     </r>
@@ -1386,6 +1502,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>社会风险治理的平台</t>
     </r>
@@ -1393,15 +1510,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>提供财产险、责任险及车险等服务，为集团重点项目配套金融支撑，统筹资本运作，充分发挥</t>
     </r>
@@ -1410,6 +1529,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>保险保障与减量</t>
     </r>
@@ -1417,15 +1537,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">秉持 </t>
     </r>
@@ -1434,6 +1556,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“诚信相伴，托付永远”</t>
     </r>
@@ -1441,6 +1564,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 使命，依托数字科技优化风控，致力于打造具有浙商特色的</t>
     </r>
@@ -1449,6 +1573,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>数字化专业保险</t>
     </r>
@@ -1456,16 +1581,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团全资金融控股管控平台</t>
     </r>
@@ -1473,6 +1600,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，成立于2018年，履行金融业务投资、管控及资产证券化等职能，促进</t>
     </r>
@@ -1481,6 +1609,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>产融深度融合</t>
     </r>
@@ -1488,15 +1617,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>提供证券、保险、资金等专业金融服务，为集团重大项目输送金融支撑，统筹产业基金运作，提供</t>
     </r>
@@ -1505,6 +1636,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>坚实资本保障</t>
     </r>
@@ -1512,15 +1644,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>以</t>
     </r>
@@ -1529,6 +1663,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>金融赋能交通产业发展</t>
     </r>
@@ -1536,6 +1671,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>为企业使命，致力于建设专业稳健、协同高效的</t>
     </r>
@@ -1544,6 +1680,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>国有金融控股平台</t>
     </r>
@@ -1551,6 +1688,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，助力主业发展。</t>
     </r>
@@ -1561,6 +1699,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团物流生态建设核心平台</t>
     </r>
@@ -1568,6 +1707,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，成立于2015年，以物流生态平台建设为核心，布局智慧园区、仓储、运输与增值服务。</t>
     </r>
@@ -1577,6 +1717,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>统筹上下游全链条开展资源组织，提供采购、仓储、运输、加工一体化供应链服务，联动集团板块</t>
     </r>
@@ -1585,6 +1726,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>深化产业协同</t>
     </r>
@@ -1592,15 +1734,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>以</t>
     </r>
@@ -1609,6 +1753,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>推动物流产业数智化升级</t>
     </r>
@@ -1616,6 +1761,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>为企业愿景，落实节能降碳举措，致力于成为国内领先的</t>
     </r>
@@ -1624,6 +1770,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>智慧物流生态组织者</t>
     </r>
@@ -1631,16 +1778,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团矿产资源投资开发主平台</t>
     </r>
@@ -1648,6 +1797,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，创建于2015年，业务覆盖战略性矿产、砂石骨料、沥青及交通新材料投资运营。</t>
     </r>
@@ -1657,6 +1807,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>整合上下游开展全链条资源组织，提供采购、加工、运输一体化服务，落实低碳循环举措，</t>
     </r>
@@ -1665,6 +1816,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>保障交通关键材料</t>
     </r>
@@ -1672,15 +1824,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">秉持 </t>
     </r>
@@ -1689,6 +1843,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“资源赋能交通，材料创造价值”</t>
     </r>
@@ -1696,6 +1851,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 使命，稳定保障交通项目供应，推动企业向</t>
     </r>
@@ -1704,6 +1860,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>科技型新材料服务商转型</t>
     </r>
@@ -1711,16 +1868,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团水上运输业务核心平台</t>
     </r>
@@ -1728,6 +1887,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，创建于1950年，拥有船队51艘、总运力约340万载重吨，航线覆盖全球主要港口。</t>
     </r>
@@ -1737,6 +1897,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>主营国内沿海运输和国际海运，运营干散货及油化品船舶；开展轻资产船队经营，推进绿色智慧航运与</t>
     </r>
@@ -1745,6 +1906,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>数字调度</t>
     </r>
@@ -1752,15 +1914,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">秉持 </t>
     </r>
@@ -1769,6 +1933,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“安全、诚信、专业、协同”</t>
     </r>
@@ -1776,6 +1941,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 核心价值观，弘扬铁一般信念，致力于为全球客户提供</t>
     </r>
@@ -1784,6 +1950,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>安全优质海上运输</t>
     </r>
@@ -1791,16 +1958,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团新供应链核心组织平台</t>
     </r>
@@ -1808,6 +1977,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，国有上市公司，聚焦大宗商品供应链集成服务，连续多年入围《财富》</t>
     </r>
@@ -1816,6 +1986,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>中国500强</t>
     </r>
@@ -1823,15 +1994,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>主营大宗商品供应链集成服务，提供采销、物流、加工一体化解决方案；深化贸工一体，依托数字天网与</t>
     </r>
@@ -1840,6 +2013,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>物流地网</t>
     </r>
@@ -1847,15 +2021,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">秉持 </t>
     </r>
@@ -1864,6 +2040,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“客户至上、开放协同、诚信担当”</t>
     </r>
@@ -1871,6 +2048,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 价值观，弘扬创业创新精神，矢志成为</t>
     </r>
@@ -1879,6 +2057,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>世界一流的产业链组织者</t>
     </r>
@@ -1886,16 +2065,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团交通数字化业务发展平台</t>
     </r>
@@ -1903,6 +2084,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，国家高新技术企业。围绕公路、轨道、机场等场景，提供数字化咨询与</t>
     </r>
@@ -1911,6 +2093,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>数据增值服务</t>
     </r>
@@ -1918,15 +2101,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>主营数字化规划咨询、数字基础设施建设、智慧高速解决方案；拓展多场景数字化建设，开展数据治理与</t>
     </r>
@@ -1935,6 +2120,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>人工智能</t>
     </r>
@@ -1942,15 +2128,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">秉持 </t>
     </r>
@@ -1959,6 +2147,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“立德守正、立业报国”</t>
     </r>
@@ -1966,6 +2155,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 核心价值观，弘扬创新精神，致力于让出行更便捷，成为</t>
     </r>
@@ -1974,6 +2164,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>数字化转型一站式服务商</t>
     </r>
@@ -1981,16 +2172,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团城市综合开发平台</t>
     </r>
@@ -1998,6 +2191,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，始创于1990年，具备房地产一级资质。在集团布局中归入新基建板块，依托交通基建统筹开发。</t>
     </r>
@@ -2007,6 +2201,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>聚焦城市综合开发与路产城融合，开展TOD、未来社区及城市更新投资建设；推进产业园区策划，</t>
     </r>
@@ -2015,6 +2210,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>提供全周期服务</t>
     </r>
@@ -2022,15 +2218,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">秉持 </t>
     </r>
@@ -2039,6 +2237,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“立德守正、立业报国”</t>
     </r>
@@ -2046,6 +2245,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 价值观，弘扬铁一般精神，致力于推动路产城融合，建设</t>
     </r>
@@ -2054,6 +2254,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>长三角领先城市运营商</t>
     </r>
@@ -2061,16 +2262,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团综合交通商业运营平台</t>
     </r>
@@ -2078,6 +2281,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，成立于1996年。以高速公路服务区为核心载体，布局综合能源、生活快消与品牌餐饮。</t>
     </r>
@@ -2087,6 +2291,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>聚焦高速服务区网络建设与运营，打造交通商业能源融合新型基础设施；推进数字化升级，构建路网服务</t>
     </r>
@@ -2095,6 +2300,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>新业态</t>
     </r>
@@ -2102,15 +2308,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">秉持 </t>
     </r>
@@ -2119,6 +2327,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“高质量服务美好出行”</t>
     </r>
@@ -2126,6 +2335,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 使命，弘扬铁一般信念与担当精神，致力于打造</t>
     </r>
@@ -2134,6 +2344,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>全国交通商业发展领跑者</t>
     </r>
@@ -2141,16 +2352,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团综合交通工程施工主力军</t>
     </r>
@@ -2158,6 +2371,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，创立于1953年，上市核心企业。业务覆盖道路、桥梁、隧道、港航、市政及轨交领域。</t>
     </r>
@@ -2167,6 +2381,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>聚焦综合交通工程施工、设计、养护全链条服务。推进工程建设与产业化贯通，深化BIM与数字孪生等</t>
     </r>
@@ -2175,6 +2390,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>数字建造技术</t>
     </r>
@@ -2182,15 +2398,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">秉持 </t>
     </r>
@@ -2199,6 +2417,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“建优质工程，创美好生活”</t>
     </r>
@@ -2206,6 +2425,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 使命，弘扬铁一般精神，致力于成为国内一流的</t>
     </r>
@@ -2214,6 +2434,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>综合交通工程承包商</t>
     </r>
@@ -2221,16 +2442,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>科技型工程咨询企业</t>
     </r>
@@ -2238,6 +2461,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，创立于1951年。集规划、勘察、设计、检测与数字化于一体，以三综甲资质支撑交通强省建设。</t>
     </r>
@@ -2247,6 +2471,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>聚焦综合交通规划咨询与勘察设计，贯通设计施工养护资源；深化BIM与智慧工地应用，推广绿色材料，</t>
     </r>
@@ -2255,6 +2480,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>打造新标杆</t>
     </r>
@@ -2262,15 +2488,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">秉持 </t>
     </r>
@@ -2279,6 +2507,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“路更畅，城更美”</t>
     </r>
@@ -2286,6 +2515,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 使命，弘扬铁一般精神，知行合一、追求卓越，致力于打造</t>
     </r>
@@ -2294,6 +2524,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>国内一流科技型工程咨询</t>
     </r>
@@ -2301,16 +2532,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>省方控股地方铁路企业</t>
     </r>
@@ -2318,6 +2551,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，成立于1992年。统筹运营金温货线等，总里程512公里，以多线合一连接浙中南与沿海港区。</t>
     </r>
@@ -2327,6 +2561,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>聚焦铁路客货运输与多线协同，开行跨局普速、动车组及市郊列车；深化铁路货运与港铁联运，打通内陆与</t>
     </r>
@@ -2335,6 +2570,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>沿海物流</t>
     </r>
@@ -2342,15 +2578,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">秉持 </t>
     </r>
@@ -2359,6 +2597,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“安全、高效、和谐、创新”</t>
     </r>
@@ -2366,6 +2605,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 价值观，弘扬拼搏奉献精神，以</t>
     </r>
@@ -2374,6 +2614,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>服务人民</t>
     </r>
@@ -2381,6 +2622,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>为使命，打造省内强劲铁路运营公司。</t>
     </r>
@@ -2391,6 +2633,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>省方铁路资本与运营专业平台</t>
     </r>
@@ -2398,6 +2641,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>。主导在建及运营多条重点铁路，以整体智治理念贯通铁路投资、建设、运营及资源开发。</t>
     </r>
@@ -2407,6 +2651,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>聚焦铁路投资资本管理、重大项目建设与全生命周期运营；深化沿线土地与产业资源综合开发，增强项目</t>
     </r>
@@ -2415,6 +2660,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>自我造血</t>
     </r>
@@ -2422,15 +2668,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">弘扬 </t>
     </r>
@@ -2439,6 +2687,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“钢铁担当，守正创新”</t>
     </r>
@@ -2446,6 +2695,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 精神，以建设共富轨道为使命，致力于打造</t>
     </r>
@@ -2454,6 +2704,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>轨道交通建设管理行业一流企业</t>
     </r>
@@ -2461,16 +2712,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>省级轨道交通统一运营试点企业</t>
     </r>
@@ -2478,6 +2731,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，成立于2017年。面向城际、市域及城市轨道交通，承担投建运维产一体化职责。</t>
     </r>
@@ -2487,6 +2741,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>聚焦轨道交通投建运维产一体化，承担多条城际与市域铁路运营组织；开展车辆智能维保检测，拓展站车资源</t>
     </r>
@@ -2495,6 +2750,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>商业开发</t>
     </r>
@@ -2502,15 +2758,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">秉持 </t>
     </r>
@@ -2519,6 +2777,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“服务人民美好出行”</t>
     </r>
@@ -2526,6 +2785,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 使命，弘扬廉能铁军精神，致力于打造价值领先的轨道交通</t>
     </r>
@@ -2534,6 +2794,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>投建运维产一体化链主</t>
     </r>
@@ -2541,16 +2802,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团高速公路建设管理平台</t>
     </r>
@@ -2558,6 +2821,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，统筹全省省级主导高速公路新建与改扩建项目。聚焦跨海桥隧等复杂工程，攻坚主力军。</t>
     </r>
@@ -2567,6 +2831,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>聚焦高速公路全周期统筹管理与复杂工程攻坚，提供一站式管控；全面推进数字建造与智慧高速应用，依托BIM与</t>
     </r>
@@ -2575,6 +2840,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>智能监测</t>
     </r>
@@ -2582,15 +2848,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">秉持 </t>
     </r>
@@ -2599,6 +2867,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“立德守正、立业报国”</t>
     </r>
@@ -2606,6 +2875,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 价值观，弘扬铁一般精神，以高标准管控为理念，打造国内一流</t>
     </r>
@@ -2614,6 +2884,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>高速智慧建设平台</t>
     </r>
@@ -2621,16 +2892,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团核心成员及境外上市平台</t>
     </r>
@@ -2638,6 +2911,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，成立于1997年。投资运营高速23条、总里程2193公里，控股浙商证券，产融协同。</t>
     </r>
@@ -2647,6 +2921,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>聚焦高速公路全周期投资运营与智慧化升级，提供收费保畅养护服务；推进数据资产入表与交能融合，探索</t>
     </r>
@@ -2655,6 +2930,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>分布式光伏</t>
     </r>
@@ -2662,15 +2938,17 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">秉持 </t>
     </r>
@@ -2679,6 +2957,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>“路通天下，融创未来”</t>
     </r>
@@ -2686,6 +2965,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 使命，弘扬乐于奉献精神，致力于打造智慧绿色、产融协同的</t>
     </r>
@@ -2694,6 +2974,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>领先基础设施运营商</t>
     </r>
@@ -2701,16 +2982,18 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>集团控股A股上市公司</t>
     </r>
@@ -2718,6 +3001,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>，形成交通工程与交通新材料双主业协同格局。承担交通工程建设、养护与新材料研发制造职责。</t>
     </r>
@@ -2727,6 +3011,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>聚焦交通工程建设、养护与新材料研发制造。贯通设计施工养护资源赋能全生命周期；深化数字建造技术应用，</t>
     </r>
@@ -2735,6 +3020,7 @@
         <b/>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>推广绿色材料</t>
     </r>
@@ -2742,6 +3028,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>。</t>
     </r>
@@ -2752,6 +3039,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>秉持“</t>
     </r>
@@ -2761,6 +3049,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>服务交通建设，推动科技兴路</t>
     </r>
@@ -2769,6 +3058,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>”使命，弘扬铁一般精神，致力于打造交通领域最具价值的</t>
     </r>
@@ -2778,6 +3068,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>一站式智慧服务平台</t>
     </r>
@@ -2786,6 +3077,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <charset val="134"/>
       </rPr>
       <t>。</t>
     </r>
@@ -2918,13 +3210,65 @@
   </si>
   <si>
     <t>audio/jkg_1.mp3</t>
+  </si>
+  <si>
+    <t>videos/zy.mp4</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>videos/gps.mp4</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>videos/jw.mp4</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>videos/kjjk.mp4</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>videos/sjt.mp4</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>videos/syjt.mp4</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>videos/sz.mp4</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>videos/hhy.mp4</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>videos/jg.mp4</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>videos/bx.mp4</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>videos/zq.mp4</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>videos/zt.mp4</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>videos/wl.mp4</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2937,31 +3281,38 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2972,6 +3323,7 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2984,12 +3336,29 @@
       <b/>
       <sz val="10"/>
       <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -3083,7 +3452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3152,6 +3521,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3456,23 +3828,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N33"/>
-  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="37.53515625" customWidth="1"/>
+    <col min="3" max="3" width="37.54296875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="13.23046875" customWidth="1"/>
-    <col min="7" max="7" width="50.15234375" customWidth="1"/>
-    <col min="8" max="8" width="42.4609375" customWidth="1"/>
-    <col min="9" max="9" width="43.07421875" customWidth="1"/>
-    <col min="10" max="10" width="42.765625" customWidth="1"/>
+    <col min="6" max="6" width="13.26953125" customWidth="1"/>
+    <col min="7" max="7" width="50.1796875" customWidth="1"/>
+    <col min="8" max="8" width="42.453125" customWidth="1"/>
+    <col min="9" max="9" width="43.08984375" customWidth="1"/>
+    <col min="10" max="10" width="42.7265625" customWidth="1"/>
     <col min="11" max="13" width="25" customWidth="1"/>
     <col min="14" max="14" width="28" customWidth="1"/>
-    <col min="15" max="16" width="9.69140625" customWidth="1"/>
+    <col min="15" max="16" width="9.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3516,7 +3888,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="42.45" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="42" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -3548,9 +3920,11 @@
       <c r="M2" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="N2" s="5"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N2" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -3574,7 +3948,7 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
@@ -3598,7 +3972,7 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>25</v>
       </c>
@@ -3622,7 +3996,7 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
@@ -3646,7 +4020,7 @@
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
@@ -3670,7 +4044,7 @@
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>31</v>
       </c>
@@ -3694,7 +4068,7 @@
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
     </row>
-    <row r="9" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
@@ -3728,9 +4102,11 @@
       <c r="M9" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="N9" s="5"/>
-    </row>
-    <row r="10" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+      <c r="N9" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
@@ -3766,7 +4142,7 @@
       </c>
       <c r="N10" s="5"/>
     </row>
-    <row r="11" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>41</v>
       </c>
@@ -3800,9 +4176,11 @@
       <c r="M11" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="N11" s="5"/>
-    </row>
-    <row r="12" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+      <c r="N11" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>44</v>
       </c>
@@ -3838,7 +4216,7 @@
       </c>
       <c r="N12" s="5"/>
     </row>
-    <row r="13" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>47</v>
       </c>
@@ -3874,7 +4252,7 @@
       </c>
       <c r="N13" s="5"/>
     </row>
-    <row r="14" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>50</v>
       </c>
@@ -3908,9 +4286,11 @@
       <c r="M14" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="N14" s="5"/>
-    </row>
-    <row r="15" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+      <c r="N14" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>53</v>
       </c>
@@ -3946,7 +4326,7 @@
       </c>
       <c r="N15" s="5"/>
     </row>
-    <row r="16" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>56</v>
       </c>
@@ -3980,9 +4360,11 @@
       <c r="M16" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="N16" s="5"/>
-    </row>
-    <row r="17" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+      <c r="N16" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>59</v>
       </c>
@@ -4016,9 +4398,11 @@
       <c r="M17" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="N17" s="5"/>
-    </row>
-    <row r="18" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+      <c r="N17" s="5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>62</v>
       </c>
@@ -4054,7 +4438,7 @@
       </c>
       <c r="N18" s="5"/>
     </row>
-    <row r="19" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>65</v>
       </c>
@@ -4088,9 +4472,11 @@
       <c r="M19" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="N19" s="5"/>
-    </row>
-    <row r="20" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+      <c r="N19" s="25" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>68</v>
       </c>
@@ -4126,7 +4512,7 @@
       </c>
       <c r="N20" s="5"/>
     </row>
-    <row r="21" spans="1:14" ht="107.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="107.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>71</v>
       </c>
@@ -4162,7 +4548,7 @@
       </c>
       <c r="N21" s="5"/>
     </row>
-    <row r="22" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>74</v>
       </c>
@@ -4196,9 +4582,11 @@
       <c r="M22" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="N22" s="5"/>
-    </row>
-    <row r="23" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+      <c r="N22" s="5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>77</v>
       </c>
@@ -4234,7 +4622,7 @@
       </c>
       <c r="N23" s="5"/>
     </row>
-    <row r="24" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>80</v>
       </c>
@@ -4270,7 +4658,7 @@
       </c>
       <c r="N24" s="5"/>
     </row>
-    <row r="25" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>84</v>
       </c>
@@ -4304,9 +4692,11 @@
       <c r="M25" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="N25" s="5"/>
-    </row>
-    <row r="26" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+      <c r="N25" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>88</v>
       </c>
@@ -4340,9 +4730,11 @@
       <c r="M26" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="N26" s="5"/>
-    </row>
-    <row r="27" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+      <c r="N26" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>92</v>
       </c>
@@ -4376,9 +4768,11 @@
       <c r="M27" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="N27" s="5"/>
-    </row>
-    <row r="28" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+      <c r="N27" s="5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>95</v>
       </c>
@@ -4412,9 +4806,11 @@
       <c r="M28" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="N28" s="5"/>
-    </row>
-    <row r="29" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+      <c r="N28" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>99</v>
       </c>
@@ -4450,7 +4846,7 @@
       </c>
       <c r="N29" s="5"/>
     </row>
-    <row r="30" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>103</v>
       </c>
@@ -4486,7 +4882,7 @@
       </c>
       <c r="N30" s="5"/>
     </row>
-    <row r="31" spans="1:14" ht="37.299999999999997" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="39" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>106</v>
       </c>
@@ -4522,7 +4918,7 @@
       </c>
       <c r="N31" s="5"/>
     </row>
-    <row r="32" spans="1:14" ht="100.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
         <v>110</v>
       </c>
@@ -4556,9 +4952,11 @@
       <c r="M32" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="N32" s="5"/>
-    </row>
-    <row r="33" spans="1:13" ht="37.299999999999997" x14ac:dyDescent="0.3">
+      <c r="N32" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="39" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>113</v>
       </c>
@@ -4593,6 +4991,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4600,7 +4999,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -4608,7 +5007,7 @@
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>116</v>
       </c>
@@ -4622,7 +5021,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>18</v>
       </c>
@@ -4636,7 +5035,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>22</v>
       </c>
@@ -4650,7 +5049,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
         <v>25</v>
       </c>
@@ -4664,7 +5063,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
         <v>27</v>
       </c>
@@ -4678,7 +5077,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
         <v>29</v>
       </c>
@@ -4692,7 +5091,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>31</v>
       </c>
@@ -4707,6 +5106,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4714,12 +5114,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z32"/>
-  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>132</v>
       </c>
@@ -4730,7 +5130,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>14</v>
       </c>
@@ -4741,7 +5141,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>14</v>
       </c>
@@ -4752,7 +5152,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
         <v>14</v>
       </c>
@@ -4763,7 +5163,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
         <v>14</v>
       </c>
@@ -4774,7 +5174,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
         <v>14</v>
       </c>
@@ -4785,7 +5185,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>14</v>
       </c>
@@ -4796,7 +5196,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
         <v>18</v>
       </c>
@@ -4807,7 +5207,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>18</v>
       </c>
@@ -4818,7 +5218,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
         <v>18</v>
       </c>
@@ -4829,7 +5229,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
         <v>18</v>
       </c>
@@ -4840,7 +5240,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
         <v>18</v>
       </c>
@@ -4851,7 +5251,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
         <v>22</v>
       </c>
@@ -4862,7 +5262,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
         <v>22</v>
       </c>
@@ -4873,7 +5273,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>22</v>
       </c>
@@ -4884,7 +5284,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
         <v>22</v>
       </c>
@@ -4895,7 +5295,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="17" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
         <v>22</v>
       </c>
@@ -4906,7 +5306,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="21" t="s">
         <v>25</v>
       </c>
@@ -4917,7 +5317,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
         <v>25</v>
       </c>
@@ -4928,7 +5328,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
         <v>25</v>
       </c>
@@ -4939,7 +5339,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="21" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>25</v>
       </c>
@@ -4950,7 +5350,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="22" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
         <v>27</v>
       </c>
@@ -4961,7 +5361,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="23" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
         <v>27</v>
       </c>
@@ -4972,7 +5372,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
         <v>27</v>
       </c>
@@ -4983,7 +5383,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="25" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
         <v>29</v>
       </c>
@@ -4994,7 +5394,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
         <v>29</v>
       </c>
@@ -5005,7 +5405,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
         <v>29</v>
       </c>
@@ -5016,7 +5416,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
         <v>31</v>
       </c>
@@ -5027,7 +5427,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
         <v>31</v>
       </c>
@@ -5038,7 +5438,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
         <v>31</v>
       </c>
@@ -5049,7 +5449,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
         <v>31</v>
       </c>
@@ -5060,7 +5460,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
         <v>22</v>
       </c>
@@ -5095,6 +5495,7 @@
       <c r="Z32" s="22"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5102,22 +5503,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>138</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>